--- a/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
+++ b/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-04T14:58:31+00:00</t>
+    <t>2026-10-06T08:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
+++ b/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T08:04:25+00:00</t>
+    <t>2026-10-06T08:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
+++ b/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T08:15:19+00:00</t>
+    <t>2026-10-13T07:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
+++ b/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:11:15+00:00</t>
+    <t>2026-10-13T07:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
+++ b/preview/pr-25/CodeSystem-mhi-chronisch.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:18:17+00:00</t>
+    <t>2026-10-13T07:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
